--- a/veterinarian_forms/013_veterinary_clinical_equipment_feedback_survey--veterinarian_forms.xlsx
+++ b/veterinarian_forms/013_veterinary_clinical_equipment_feedback_survey--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_01'}</t>
+          <t>equipment_used_today_01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_01'}</t>
+          <t>equipment used today 01</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_02'}</t>
+          <t>equipment_used_today_02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_02'}</t>
+          <t>equipment used today 02</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_03'}</t>
+          <t>equipment_used_today_03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_03'}</t>
+          <t>equipment used today 03</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_04'}</t>
+          <t>equipment_used_today_04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_04'}</t>
+          <t>equipment used today 04</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_05'}</t>
+          <t>equipment_used_today_05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_05'}</t>
+          <t>equipment used today 05</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_06'}</t>
+          <t>equipment_used_today_06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_06'}</t>
+          <t>equipment used today 06</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_07'}</t>
+          <t>equipment_used_today_07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_07'}</t>
+          <t>equipment used today 07</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_08'}</t>
+          <t>equipment_used_today_08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_08'}</t>
+          <t>equipment used today 08</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_09'}</t>
+          <t>equipment_used_today_09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_09'}</t>
+          <t>equipment used today 09</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_used_today_10'}</t>
+          <t>equipment_used_today_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_used_today_10'}</t>
+          <t>equipment used today 10</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_condition_01'}</t>
+          <t>equipment_condition_01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_condition_01'}</t>
+          <t>equipment condition 01</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_condition_02'}</t>
+          <t>equipment_condition_02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_condition_02'}</t>
+          <t>equipment condition 02</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_condition_03'}</t>
+          <t>equipment_condition_03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_condition_03'}</t>
+          <t>equipment condition 03</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_condition_04'}</t>
+          <t>equipment_condition_04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_condition_04'}</t>
+          <t>equipment condition 04</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_condition_05'}</t>
+          <t>equipment_condition_05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_condition_05'}</t>
+          <t>equipment condition 05</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_condition_06'}</t>
+          <t>equipment_condition_06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_condition_06'}</t>
+          <t>equipment condition 06</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_condition_07'}</t>
+          <t>equipment_condition_07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_condition_07'}</t>
+          <t>equipment condition 07</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_01'}</t>
+          <t>ease_of_use_01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_01'}</t>
+          <t>ease of use 01</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_02'}</t>
+          <t>ease_of_use_02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_02'}</t>
+          <t>ease of use 02</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_03'}</t>
+          <t>ease_of_use_03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_03'}</t>
+          <t>ease of use 03</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_04'}</t>
+          <t>ease_of_use_04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_04'}</t>
+          <t>ease of use 04</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_05'}</t>
+          <t>ease_of_use_05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_05'}</t>
+          <t>ease of use 05</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_06'}</t>
+          <t>ease_of_use_06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_06'}</t>
+          <t>ease of use 06</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_07'}</t>
+          <t>ease_of_use_07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_07'}</t>
+          <t>ease of use 07</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'ease_of_use_08'}</t>
+          <t>ease_of_use_08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'ease_of_use_08'}</t>
+          <t>ease of use 08</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'overall_experience_01'}</t>
+          <t>overall_experience_01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'overall_experience_01'}</t>
+          <t>overall experience 01</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'overall_experience_02'}</t>
+          <t>overall_experience_02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'overall_experience_02'}</t>
+          <t>overall experience 02</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'overall_experience_03'}</t>
+          <t>overall_experience_03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'overall_experience_03'}</t>
+          <t>overall experience 03</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'overall_experience_04'}</t>
+          <t>overall_experience_04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'overall_experience_04'}</t>
+          <t>overall experience 04</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'overall_experience_05'}</t>
+          <t>overall_experience_05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'overall_experience_05'}</t>
+          <t>overall experience 05</t>
         </is>
       </c>
     </row>
